--- a/scanlag_data/CASP+SHX/scanlag_summary.xlsx
+++ b/scanlag_data/CASP+SHX/scanlag_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Projects\manuscript_reviews\scanlag_data\CASP+SHX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81C0148-5720-49E1-A270-30C3D6EFBD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C616A87A-0BF6-49EC-9290-D298D1D8A8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DEF8DDA-6DDB-4E4E-9FF3-E592AEBCB150}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>MG1655</t>
   </si>
   <si>
-    <t>VapC 2h</t>
-  </si>
-  <si>
     <t>VapC 24h</t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>VapC 4h</t>
   </si>
 </sst>
 </file>
@@ -508,13 +508,13 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -563,13 +563,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -581,22 +581,22 @@
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
         <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
       </c>
       <c r="K3" t="s">
         <v>9</v>
       </c>
       <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
         <v>14</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -747,7 +747,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
